--- a/Delhi-June-2025.xlsx
+++ b/Delhi-June-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="82">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Delhi</t>
   </si>
   <si>
@@ -106,10 +109,10 @@
     <t>MH02FG7557</t>
   </si>
   <si>
-    <t>DL1NA-3869</t>
-  </si>
-  <si>
-    <t>DL1NA-3910</t>
+    <t>DL1NA3869</t>
+  </si>
+  <si>
+    <t>DL1NA3910</t>
   </si>
   <si>
     <t>HR38AD1176</t>
@@ -130,13 +133,13 @@
     <t>HR38AE5738</t>
   </si>
   <si>
-    <t>HR38Y-6988</t>
-  </si>
-  <si>
-    <t>HR55AR-0857</t>
-  </si>
-  <si>
-    <t>HR55AR-1793</t>
+    <t>HR38Y6988</t>
+  </si>
+  <si>
+    <t>HR55AR0857</t>
+  </si>
+  <si>
+    <t>HR55AR1793</t>
   </si>
   <si>
     <t>MH02ER7925</t>
@@ -172,7 +175,7 @@
     <t>HR55AX6981</t>
   </si>
   <si>
-    <t>DL1N-6505</t>
+    <t>DL1N6505</t>
   </si>
   <si>
     <t>HR38AE9224</t>
@@ -199,13 +202,13 @@
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>Dzire</t>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>ETIOS</t>
@@ -218,6 +221,42 @@
   </si>
   <si>
     <t>URBANIA</t>
+  </si>
+  <si>
+    <t>25/01/2024</t>
+  </si>
+  <si>
+    <t>17/08/2022</t>
+  </si>
+  <si>
+    <t>21/04/2023</t>
+  </si>
+  <si>
+    <t>16/08/2018</t>
+  </si>
+  <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>21/04/2014</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
   </si>
   <si>
     <t>-</t>
@@ -227,6 +266,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -279,11 +321,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,10 +621,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,28 +703,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2">
-        <v>45316</v>
+        <v>60</v>
+      </c>
+      <c r="G2" t="s">
+        <v>69</v>
       </c>
       <c r="H2">
         <v>48166</v>
@@ -741,27 +787,27 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <v>44719</v>
+        <v>61</v>
+      </c>
+      <c r="G3" s="2">
+        <v>44748</v>
       </c>
       <c r="H3">
         <v>29384</v>
@@ -821,27 +867,27 @@
         <v>-188.76</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="G4" s="2">
+        <v>43565</v>
       </c>
       <c r="H4">
         <v>215285</v>
@@ -901,27 +947,27 @@
         <v>53.27</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43565</v>
       </c>
       <c r="H5">
         <v>215680</v>
@@ -981,27 +1027,27 @@
         <v>58.45</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6">
-        <v>44790</v>
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
       </c>
       <c r="H6">
         <v>198974</v>
@@ -1061,27 +1107,27 @@
         <v>45.63</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>44816</v>
+        <v>62</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44904</v>
       </c>
       <c r="H7">
         <v>127095</v>
@@ -1141,27 +1187,27 @@
         <v>53.87</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8">
-        <v>44790</v>
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
       </c>
       <c r="H8">
         <v>154439</v>
@@ -1221,27 +1267,27 @@
         <v>60.21</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>44816</v>
+        <v>62</v>
+      </c>
+      <c r="G9" s="2">
+        <v>44904</v>
       </c>
       <c r="H9">
         <v>135505</v>
@@ -1301,27 +1347,27 @@
         <v>47.29</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
-        <v>45037</v>
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>71</v>
       </c>
       <c r="H10">
         <v>107259</v>
@@ -1381,27 +1427,27 @@
         <v>16.99</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>45037</v>
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
       </c>
       <c r="H11">
         <v>104899</v>
@@ -1461,27 +1507,27 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H12">
         <v>115617</v>
@@ -1541,27 +1587,27 @@
         <v>49.45</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H13">
         <v>78757</v>
@@ -1621,27 +1667,27 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H14">
         <v>94580</v>
@@ -1701,27 +1747,27 @@
         <v>21.29</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="G15" s="2">
+        <v>43587</v>
       </c>
       <c r="H15">
         <v>181085</v>
@@ -1781,27 +1827,27 @@
         <v>57.64</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>44236</v>
+        <v>62</v>
+      </c>
+      <c r="G16" s="2">
+        <v>44441</v>
       </c>
       <c r="H16">
         <v>104800</v>
@@ -1866,22 +1912,22 @@
         <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
-        <v>44280</v>
+        <v>62</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
       </c>
       <c r="H17">
         <v>83973</v>
@@ -1946,22 +1992,22 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
-        <v>44460</v>
+        <v>62</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
       </c>
       <c r="H18">
         <v>96221</v>
@@ -2026,22 +2072,22 @@
         <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>44490</v>
+        <v>62</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
       </c>
       <c r="H19">
         <v>80402</v>
@@ -2106,22 +2152,22 @@
         <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>44807</v>
+        <v>62</v>
+      </c>
+      <c r="G20" s="2">
+        <v>44629</v>
       </c>
       <c r="H20">
         <v>50296</v>
@@ -2186,22 +2232,22 @@
         <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>45293</v>
+        <v>63</v>
+      </c>
+      <c r="G21" s="2">
+        <v>45323</v>
       </c>
       <c r="H21">
         <v>34167</v>
@@ -2266,22 +2312,22 @@
         <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H22">
         <v>37</v>
@@ -2346,22 +2392,22 @@
         <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2415,7 +2461,7 @@
         <v>-4361</v>
       </c>
       <c r="Z23" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:26">
@@ -2423,22 +2469,22 @@
         <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24">
-        <v>45820</v>
+        <v>64</v>
+      </c>
+      <c r="G24" s="2">
+        <v>45997</v>
       </c>
       <c r="H24">
         <v>112</v>
@@ -2503,22 +2549,22 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25">
-        <v>45820</v>
+        <v>64</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45997</v>
       </c>
       <c r="H25">
         <v>190</v>
@@ -2583,22 +2629,22 @@
         <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2652,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -2660,22 +2706,22 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>44999</v>
+        <v>66</v>
+      </c>
+      <c r="G27" t="s">
+        <v>79</v>
       </c>
       <c r="H27">
         <v>101231</v>
@@ -2740,22 +2786,22 @@
         <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>45510</v>
+        <v>67</v>
+      </c>
+      <c r="G28" s="2">
+        <v>45451</v>
       </c>
       <c r="H28">
         <v>28486</v>
@@ -2820,22 +2866,22 @@
         <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
-        <v>45510</v>
+        <v>67</v>
+      </c>
+      <c r="G29" s="2">
+        <v>45451</v>
       </c>
       <c r="H29">
         <v>30605</v>
@@ -2900,22 +2946,22 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>45481</v>
+        <v>67</v>
+      </c>
+      <c r="G30" s="2">
+        <v>45511</v>
       </c>
       <c r="H30">
         <v>32073</v>
@@ -2980,22 +3026,22 @@
         <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>45481</v>
+        <v>67</v>
+      </c>
+      <c r="G31" s="2">
+        <v>45511</v>
       </c>
       <c r="H31">
         <v>34495</v>
@@ -3060,22 +3106,22 @@
         <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32">
-        <v>45680</v>
+        <v>68</v>
+      </c>
+      <c r="G32" t="s">
+        <v>80</v>
       </c>
       <c r="H32">
         <v>4016</v>
